--- a/backend/data/financials_by_company/1CG.AX.xlsx
+++ b/backend/data/financials_by_company/1CG.AX.xlsx
@@ -3423,10 +3423,8 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>6008</t>
-        </is>
+      <c r="E2" t="n">
+        <v>6008</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -3612,7 +3610,7 @@
         <v>-716460</v>
       </c>
       <c r="BG2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BH2" t="n">
         <v>1.886</v>
@@ -3841,7 +3839,7 @@
         <v>17.647064</v>
       </c>
       <c r="DR2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DS2" t="n">
         <v>0</v>
